--- a/docs/候補地スクリーニング_秋田30件.xlsx
+++ b/docs/候補地スクリーニング_秋田30件.xlsx
@@ -11,7 +11,7 @@
     <sheet name="読み方・出典" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'スクリーニング'!$A$2:$V$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'スクリーニング'!$A$2:$AD$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:AD75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -464,16 +464,24 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="7" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,50 +554,96 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>空容量
+上位系MW</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>空容量
+当該MW</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>採用空容量
+MW</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>運用容量
+MW</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>予想潮流
+MW</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>N-1電制</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>出力制御</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>二次電圧
+kV</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
           <t>系統(80)</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>S7(20)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>総合(100)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>ランク</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>洪水浸水(想定最大)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>津波浸水想定</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>高潮浸水想定</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>土砂災害(土石流)</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>土砂災害(急傾斜)</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>土砂災害(地すべり)</t>
         </is>
@@ -648,46 +702,68 @@
           <t>591 m</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-15</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
         <v>48</v>
       </c>
-      <c r="N3" t="n">
+      <c r="V3" t="n">
         <v>15</v>
       </c>
-      <c r="O3" t="n">
+      <c r="W3" t="n">
         <v>63</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -746,46 +822,68 @@
           <t>6.17 km</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O4" t="n">
+        <v>19</v>
+      </c>
+      <c r="P4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
         <v>41</v>
       </c>
-      <c r="N4" t="n">
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
+      <c r="W4" t="n">
         <v>41</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -816,26 +914,48 @@
           <t>7.05 km</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
         <v>41</v>
       </c>
-      <c r="N5" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
+      <c r="W5" t="n">
         <v>41</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -862,26 +982,48 @@
           <t>7.05 km</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>36</v>
       </c>
-      <c r="N6" t="n">
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
+      <c r="W6" t="n">
         <v>36</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -936,46 +1078,71 @@
           <t>499 m</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>58</v>
-      </c>
       <c r="N7" t="n">
         <v>20</v>
       </c>
       <c r="O7" t="n">
+        <v>20</v>
+      </c>
+      <c r="P7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>58</v>
+      </c>
+      <c r="V7" t="n">
+        <v>20</v>
+      </c>
+      <c r="W7" t="n">
         <v>78</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -1006,26 +1173,51 @@
           <t>3.28 km</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>31</v>
+      </c>
+      <c r="O8" t="n">
+        <v>31</v>
+      </c>
+      <c r="P8" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-23</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U8" t="n">
         <v>58</v>
       </c>
-      <c r="N8" t="n">
+      <c r="V8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" t="n">
+      <c r="W8" t="n">
         <v>62</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1052,26 +1244,51 @@
           <t>1.96 km</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>16</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-38</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U9" t="n">
         <v>46</v>
       </c>
-      <c r="N9" t="n">
+      <c r="V9" t="n">
         <v>10</v>
       </c>
-      <c r="O9" t="n">
+      <c r="W9" t="n">
         <v>56</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1126,46 +1343,71 @@
           <t>5.82 km</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>31</v>
+      </c>
+      <c r="O10" t="n">
+        <v>31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-23</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U10" t="n">
         <v>58</v>
       </c>
-      <c r="N10" t="n">
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="n">
+      <c r="W10" t="n">
         <v>58</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -1196,26 +1438,51 @@
           <t>8.46 km</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P11" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U11" t="n">
         <v>58</v>
       </c>
-      <c r="N11" t="n">
+      <c r="V11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="n">
+      <c r="W11" t="n">
         <v>58</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1242,26 +1509,51 @@
           <t>6.34 km</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U12" t="n">
         <v>51</v>
       </c>
-      <c r="N12" t="n">
+      <c r="V12" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="n">
+      <c r="W12" t="n">
         <v>51</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1316,46 +1608,68 @@
           <t>3.43 km</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>21</v>
+      </c>
+      <c r="O13" t="n">
+        <v>21</v>
+      </c>
+      <c r="P13" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
         <v>43</v>
       </c>
-      <c r="N13" t="n">
+      <c r="V13" t="n">
         <v>4</v>
       </c>
-      <c r="O13" t="n">
+      <c r="W13" t="n">
         <v>47</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -1386,26 +1700,48 @@
           <t>7.10 km</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>17</v>
+      </c>
+      <c r="O14" t="n">
+        <v>17</v>
+      </c>
+      <c r="P14" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
         <v>41</v>
       </c>
-      <c r="N14" t="n">
+      <c r="V14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
+      <c r="W14" t="n">
         <v>41</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1432,26 +1768,48 @@
           <t>8.49 km</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
         <v>41</v>
       </c>
-      <c r="N15" t="n">
+      <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
+      <c r="W15" t="n">
         <v>41</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1506,46 +1864,68 @@
           <t>2.84 km</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>11</v>
+      </c>
+      <c r="O16" t="n">
+        <v>11</v>
+      </c>
+      <c r="P16" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-29</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
         <v>36</v>
       </c>
-      <c r="N16" t="n">
+      <c r="V16" t="n">
         <v>4</v>
       </c>
-      <c r="O16" t="n">
+      <c r="W16" t="n">
         <v>40</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="Y16" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -1576,26 +1956,48 @@
           <t>6.37 km</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-40</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
         <v>23</v>
       </c>
-      <c r="N17" t="n">
+      <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="n">
+      <c r="W17" t="n">
         <v>23</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1622,26 +2024,48 @@
           <t>9.72 km</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-12</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
         <v>23</v>
       </c>
-      <c r="N18" t="n">
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="n">
+      <c r="W18" t="n">
         <v>23</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1696,46 +2120,68 @@
           <t>1.86 km</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>11</v>
+      </c>
+      <c r="O19" t="n">
+        <v>11</v>
+      </c>
+      <c r="P19" t="n">
         <v>36</v>
       </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>36</v>
+      </c>
+      <c r="V19" t="n">
         <v>10</v>
       </c>
-      <c r="O19" t="n">
+      <c r="W19" t="n">
         <v>46</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -1766,26 +2212,48 @@
           <t>7.46 km</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>11</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11</v>
+      </c>
+      <c r="P20" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
         <v>36</v>
       </c>
-      <c r="N20" t="n">
+      <c r="V20" t="n">
         <v>0</v>
       </c>
-      <c r="O20" t="n">
+      <c r="W20" t="n">
         <v>36</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1840,46 +2308,68 @@
           <t>7.74 km</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>20</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
         <v>48</v>
       </c>
-      <c r="N21" t="n">
+      <c r="V21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="n">
+      <c r="W21" t="n">
         <v>48</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -1938,46 +2428,68 @@
           <t>1.45 km</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>11</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11</v>
+      </c>
+      <c r="P22" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
         <v>36</v>
       </c>
-      <c r="N22" t="n">
+      <c r="V22" t="n">
         <v>10</v>
       </c>
-      <c r="O22" t="n">
+      <c r="W22" t="n">
         <v>46</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z22" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -2008,26 +2520,48 @@
           <t>1.94 km</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>12</v>
+      </c>
+      <c r="P23" t="n">
         <v>36</v>
       </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
+        <v>-24</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>36</v>
+      </c>
+      <c r="V23" t="n">
         <v>10</v>
       </c>
-      <c r="O23" t="n">
+      <c r="W23" t="n">
         <v>46</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2082,46 +2616,68 @@
           <t>1.33 km</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O24" t="n">
+        <v>11</v>
+      </c>
+      <c r="P24" t="n">
         <v>36</v>
       </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>36</v>
+      </c>
+      <c r="V24" t="n">
         <v>10</v>
       </c>
-      <c r="O24" t="n">
+      <c r="W24" t="n">
         <v>46</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -2152,26 +2708,48 @@
           <t>7.97 km</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>11</v>
+      </c>
+      <c r="O25" t="n">
+        <v>11</v>
+      </c>
+      <c r="P25" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-20</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
         <v>36</v>
       </c>
-      <c r="N25" t="n">
+      <c r="V25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="n">
+      <c r="W25" t="n">
         <v>36</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2226,46 +2804,68 @@
           <t>2.61 km</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
+        <v>11</v>
+      </c>
+      <c r="O26" t="n">
+        <v>11</v>
+      </c>
+      <c r="P26" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
         <v>36</v>
       </c>
-      <c r="N26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="W26" t="n">
         <v>40</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -2296,26 +2896,48 @@
           <t>5.54 km</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
+        <v>12</v>
+      </c>
+      <c r="O27" t="n">
+        <v>12</v>
+      </c>
+      <c r="P27" t="n">
         <v>36</v>
       </c>
-      <c r="N27" t="n">
+      <c r="Q27" t="n">
+        <v>-24</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>36</v>
+      </c>
+      <c r="V27" t="n">
         <v>0</v>
       </c>
-      <c r="O27" t="n">
+      <c r="W27" t="n">
         <v>36</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2342,26 +2964,48 @@
           <t>9.45 km</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-27</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
         <v>23</v>
       </c>
-      <c r="N28" t="n">
+      <c r="V28" t="n">
         <v>0</v>
       </c>
-      <c r="O28" t="n">
+      <c r="W28" t="n">
         <v>23</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2416,46 +3060,68 @@
           <t>4.87 km</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
+        <v>20</v>
+      </c>
+      <c r="O29" t="n">
+        <v>20</v>
+      </c>
+      <c r="P29" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
         <v>48</v>
       </c>
-      <c r="N29" t="n">
+      <c r="V29" t="n">
         <v>4</v>
       </c>
-      <c r="O29" t="n">
+      <c r="W29" t="n">
         <v>52</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -2514,46 +3180,68 @@
           <t>3.31 km</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>21</v>
+      </c>
+      <c r="O30" t="n">
+        <v>21</v>
+      </c>
+      <c r="P30" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
         <v>43</v>
       </c>
-      <c r="N30" t="n">
+      <c r="V30" t="n">
         <v>4</v>
       </c>
-      <c r="O30" t="n">
+      <c r="W30" t="n">
         <v>47</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -2584,26 +3272,48 @@
           <t>2.56 km</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>15</v>
+      </c>
+      <c r="P31" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
         <v>41</v>
       </c>
-      <c r="N31" t="n">
+      <c r="V31" t="n">
         <v>4</v>
       </c>
-      <c r="O31" t="n">
+      <c r="W31" t="n">
         <v>45</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2658,46 +3368,68 @@
           <t>2.29 km</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>11</v>
+      </c>
+      <c r="O32" t="n">
+        <v>11</v>
+      </c>
+      <c r="P32" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
         <v>36</v>
       </c>
-      <c r="N32" t="n">
+      <c r="V32" t="n">
         <v>4</v>
       </c>
-      <c r="O32" t="n">
+      <c r="W32" t="n">
         <v>40</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -2728,26 +3460,48 @@
           <t>4.90 km</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
+        <v>12</v>
+      </c>
+      <c r="O33" t="n">
+        <v>12</v>
+      </c>
+      <c r="P33" t="n">
         <v>36</v>
       </c>
-      <c r="N33" t="n">
+      <c r="Q33" t="n">
+        <v>-24</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>36</v>
+      </c>
+      <c r="V33" t="n">
         <v>4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="W33" t="n">
         <v>40</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2802,46 +3556,71 @@
           <t>6.52 km</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>31</v>
+      </c>
+      <c r="O34" t="n">
+        <v>31</v>
+      </c>
+      <c r="P34" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-23</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U34" t="n">
         <v>58</v>
       </c>
-      <c r="N34" t="n">
+      <c r="V34" t="n">
         <v>0</v>
       </c>
-      <c r="O34" t="n">
+      <c r="W34" t="n">
         <v>58</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -2872,26 +3651,51 @@
           <t>9.04 km</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
+        <v>20</v>
+      </c>
+      <c r="O35" t="n">
+        <v>20</v>
+      </c>
+      <c r="P35" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U35" t="n">
         <v>58</v>
       </c>
-      <c r="N35" t="n">
+      <c r="V35" t="n">
         <v>0</v>
       </c>
-      <c r="O35" t="n">
+      <c r="W35" t="n">
         <v>58</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2918,26 +3722,51 @@
           <t>6.69 km</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
+        <v>11</v>
+      </c>
+      <c r="O36" t="n">
+        <v>11</v>
+      </c>
+      <c r="P36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U36" t="n">
         <v>51</v>
       </c>
-      <c r="N36" t="n">
+      <c r="V36" t="n">
         <v>0</v>
       </c>
-      <c r="O36" t="n">
+      <c r="W36" t="n">
         <v>51</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2992,46 +3821,68 @@
           <t>1.57 km</t>
         </is>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
+        <v>15</v>
+      </c>
+      <c r="O37" t="n">
+        <v>15</v>
+      </c>
+      <c r="P37" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
         <v>41</v>
       </c>
-      <c r="N37" t="n">
+      <c r="V37" t="n">
         <v>10</v>
       </c>
-      <c r="O37" t="n">
+      <c r="W37" t="n">
         <v>51</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -3062,26 +3913,48 @@
           <t>4.68 km</t>
         </is>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
+        <v>21</v>
+      </c>
+      <c r="O38" t="n">
+        <v>21</v>
+      </c>
+      <c r="P38" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
         <v>43</v>
       </c>
-      <c r="N38" t="n">
+      <c r="V38" t="n">
         <v>4</v>
       </c>
-      <c r="O38" t="n">
+      <c r="W38" t="n">
         <v>47</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3136,46 +4009,68 @@
           <t>1.43 km</t>
         </is>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
+        <v>17</v>
+      </c>
+      <c r="O39" t="n">
+        <v>17</v>
+      </c>
+      <c r="P39" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
         <v>41</v>
       </c>
-      <c r="N39" t="n">
+      <c r="V39" t="n">
         <v>10</v>
       </c>
-      <c r="O39" t="n">
+      <c r="W39" t="n">
         <v>51</v>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q39" s="4" t="inlineStr">
+      <c r="Y39" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -3206,26 +4101,48 @@
           <t>7.18 km</t>
         </is>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
+        <v>15</v>
+      </c>
+      <c r="O40" t="n">
+        <v>15</v>
+      </c>
+      <c r="P40" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-34</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
         <v>36</v>
       </c>
-      <c r="N40" t="n">
+      <c r="V40" t="n">
         <v>0</v>
       </c>
-      <c r="O40" t="n">
+      <c r="W40" t="n">
         <v>36</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3280,46 +4197,68 @@
           <t>8.93 km</t>
         </is>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
+        <v>19</v>
+      </c>
+      <c r="O41" t="n">
+        <v>19</v>
+      </c>
+      <c r="P41" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>-17</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
         <v>41</v>
       </c>
-      <c r="N41" t="n">
+      <c r="V41" t="n">
         <v>0</v>
       </c>
-      <c r="O41" t="n">
+      <c r="W41" t="n">
         <v>41</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q41" s="4" t="inlineStr">
+      <c r="Y41" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -3350,26 +4289,48 @@
           <t>2.54 km</t>
         </is>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
+        <v>15</v>
+      </c>
+      <c r="O42" t="n">
+        <v>15</v>
+      </c>
+      <c r="P42" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>-34</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
         <v>36</v>
       </c>
-      <c r="N42" t="n">
+      <c r="V42" t="n">
         <v>4</v>
       </c>
-      <c r="O42" t="n">
+      <c r="W42" t="n">
         <v>40</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3424,46 +4385,68 @@
           <t>6.44 km</t>
         </is>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
+        <v>7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>7</v>
+      </c>
+      <c r="P43" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>-11</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
         <v>36</v>
       </c>
-      <c r="N43" t="n">
+      <c r="V43" t="n">
         <v>0</v>
       </c>
-      <c r="O43" t="n">
+      <c r="W43" t="n">
         <v>36</v>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R43" s="4" t="inlineStr">
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z43" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -3494,26 +4477,48 @@
           <t>2.22 km</t>
         </is>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2</v>
+      </c>
+      <c r="P44" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-38</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
         <v>19</v>
       </c>
-      <c r="N44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
-      <c r="O44" t="n">
+      <c r="W44" t="n">
         <v>23</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3568,46 +4573,68 @@
           <t>6.32 km</t>
         </is>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
+        <v>11</v>
+      </c>
+      <c r="O45" t="n">
+        <v>11</v>
+      </c>
+      <c r="P45" t="n">
         <v>36</v>
       </c>
-      <c r="N45" t="n">
+      <c r="Q45" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>36</v>
+      </c>
+      <c r="V45" t="n">
         <v>0</v>
       </c>
-      <c r="O45" t="n">
+      <c r="W45" t="n">
         <v>36</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -3638,26 +4665,48 @@
           <t>6.38 km</t>
         </is>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>-38</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
         <v>19</v>
       </c>
-      <c r="N46" t="n">
+      <c r="V46" t="n">
         <v>0</v>
       </c>
-      <c r="O46" t="n">
+      <c r="W46" t="n">
         <v>19</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3712,46 +4761,71 @@
           <t>9.40 km</t>
         </is>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
+        <v>31</v>
+      </c>
+      <c r="O47" t="n">
+        <v>31</v>
+      </c>
+      <c r="P47" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-23</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U47" t="n">
         <v>58</v>
       </c>
-      <c r="N47" t="n">
+      <c r="V47" t="n">
         <v>0</v>
       </c>
-      <c r="O47" t="n">
+      <c r="W47" t="n">
         <v>58</v>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="inlineStr">
+      <c r="Y47" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -3782,26 +4856,51 @@
           <t>9.60 km</t>
         </is>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
+        <v>11</v>
+      </c>
+      <c r="O48" t="n">
+        <v>11</v>
+      </c>
+      <c r="P48" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U48" t="n">
         <v>51</v>
       </c>
-      <c r="N48" t="n">
+      <c r="V48" t="n">
         <v>0</v>
       </c>
-      <c r="O48" t="n">
+      <c r="W48" t="n">
         <v>51</v>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3828,26 +4927,48 @@
           <t>8.93 km</t>
         </is>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
+        <v>23</v>
+      </c>
+      <c r="O49" t="n">
+        <v>23</v>
+      </c>
+      <c r="P49" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-13</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
         <v>48</v>
       </c>
-      <c r="N49" t="n">
+      <c r="V49" t="n">
         <v>0</v>
       </c>
-      <c r="O49" t="n">
+      <c r="W49" t="n">
         <v>48</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3902,46 +5023,68 @@
           <t>448 m</t>
         </is>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
+        <v>11</v>
+      </c>
+      <c r="O50" t="n">
+        <v>11</v>
+      </c>
+      <c r="P50" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-29</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
         <v>36</v>
       </c>
-      <c r="N50" t="n">
+      <c r="V50" t="n">
         <v>20</v>
       </c>
-      <c r="O50" t="n">
+      <c r="W50" t="n">
         <v>56</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -3972,26 +5115,48 @@
           <t>4.18 km</t>
         </is>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5</v>
+      </c>
+      <c r="P51" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-40</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
         <v>23</v>
       </c>
-      <c r="N51" t="n">
+      <c r="V51" t="n">
         <v>4</v>
       </c>
-      <c r="O51" t="n">
+      <c r="W51" t="n">
         <v>27</v>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -4018,26 +5183,48 @@
           <t>7.87 km</t>
         </is>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2</v>
+      </c>
+      <c r="P52" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-12</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
         <v>23</v>
       </c>
-      <c r="N52" t="n">
+      <c r="V52" t="n">
         <v>0</v>
       </c>
-      <c r="O52" t="n">
+      <c r="W52" t="n">
         <v>23</v>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -4092,46 +5279,71 @@
           <t>4.12 km</t>
         </is>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
+        <v>31</v>
+      </c>
+      <c r="O53" t="n">
+        <v>31</v>
+      </c>
+      <c r="P53" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-23</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U53" t="n">
         <v>58</v>
       </c>
-      <c r="N53" t="n">
+      <c r="V53" t="n">
         <v>4</v>
       </c>
-      <c r="O53" t="n">
+      <c r="W53" t="n">
         <v>62</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q53" s="4" t="inlineStr">
+      <c r="Y53" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -4162,26 +5374,51 @@
           <t>6.42 km</t>
         </is>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
+        <v>20</v>
+      </c>
+      <c r="O54" t="n">
+        <v>20</v>
+      </c>
+      <c r="P54" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U54" t="n">
         <v>58</v>
       </c>
-      <c r="N54" t="n">
+      <c r="V54" t="n">
         <v>0</v>
       </c>
-      <c r="O54" t="n">
+      <c r="W54" t="n">
         <v>58</v>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -4208,26 +5445,51 @@
           <t>4.38 km</t>
         </is>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
+        <v>11</v>
+      </c>
+      <c r="O55" t="n">
+        <v>11</v>
+      </c>
+      <c r="P55" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U55" t="n">
         <v>51</v>
       </c>
-      <c r="N55" t="n">
+      <c r="V55" t="n">
         <v>4</v>
       </c>
-      <c r="O55" t="n">
+      <c r="W55" t="n">
         <v>55</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -4282,46 +5544,71 @@
           <t>4.05 km</t>
         </is>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
+        <v>31</v>
+      </c>
+      <c r="O56" t="n">
+        <v>31</v>
+      </c>
+      <c r="P56" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-23</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U56" t="n">
         <v>58</v>
       </c>
-      <c r="N56" t="n">
+      <c r="V56" t="n">
         <v>4</v>
       </c>
-      <c r="O56" t="n">
+      <c r="W56" t="n">
         <v>62</v>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q56" s="4" t="inlineStr">
+      <c r="Y56" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -4352,26 +5639,51 @@
           <t>6.00 km</t>
         </is>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
+        <v>20</v>
+      </c>
+      <c r="O57" t="n">
+        <v>20</v>
+      </c>
+      <c r="P57" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U57" t="n">
         <v>58</v>
       </c>
-      <c r="N57" t="n">
+      <c r="V57" t="n">
         <v>0</v>
       </c>
-      <c r="O57" t="n">
+      <c r="W57" t="n">
         <v>58</v>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -4398,26 +5710,51 @@
           <t>3.70 km</t>
         </is>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
+        <v>11</v>
+      </c>
+      <c r="O58" t="n">
+        <v>11</v>
+      </c>
+      <c r="P58" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U58" t="n">
         <v>51</v>
       </c>
-      <c r="N58" t="n">
+      <c r="V58" t="n">
         <v>4</v>
       </c>
-      <c r="O58" t="n">
+      <c r="W58" t="n">
         <v>55</v>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4472,46 +5809,68 @@
           <t>2.08 km</t>
         </is>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
+        <v>11</v>
+      </c>
+      <c r="O59" t="n">
+        <v>11</v>
+      </c>
+      <c r="P59" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>-29</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
         <v>36</v>
       </c>
-      <c r="N59" t="n">
+      <c r="V59" t="n">
         <v>4</v>
       </c>
-      <c r="O59" t="n">
+      <c r="W59" t="n">
         <v>40</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -4542,26 +5901,48 @@
           <t>3.85 km</t>
         </is>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
+        <v>5</v>
+      </c>
+      <c r="O60" t="n">
+        <v>5</v>
+      </c>
+      <c r="P60" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>-40</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
         <v>23</v>
       </c>
-      <c r="N60" t="n">
+      <c r="V60" t="n">
         <v>4</v>
       </c>
-      <c r="O60" t="n">
+      <c r="W60" t="n">
         <v>27</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -4588,26 +5969,48 @@
           <t>5.82 km</t>
         </is>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2</v>
+      </c>
+      <c r="P61" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>-12</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
         <v>23</v>
       </c>
-      <c r="N61" t="n">
+      <c r="V61" t="n">
         <v>0</v>
       </c>
-      <c r="O61" t="n">
+      <c r="W61" t="n">
         <v>23</v>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4662,46 +6065,68 @@
           <t>2.27 km</t>
         </is>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
+        <v>21</v>
+      </c>
+      <c r="O62" t="n">
+        <v>21</v>
+      </c>
+      <c r="P62" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
         <v>43</v>
       </c>
-      <c r="N62" t="n">
+      <c r="V62" t="n">
         <v>4</v>
       </c>
-      <c r="O62" t="n">
+      <c r="W62" t="n">
         <v>47</v>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -4732,26 +6157,48 @@
           <t>5.56 km</t>
         </is>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
+        <v>15</v>
+      </c>
+      <c r="O63" t="n">
+        <v>15</v>
+      </c>
+      <c r="P63" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
         <v>41</v>
       </c>
-      <c r="N63" t="n">
+      <c r="V63" t="n">
         <v>0</v>
       </c>
-      <c r="O63" t="n">
+      <c r="W63" t="n">
         <v>41</v>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -4778,26 +6225,48 @@
           <t>9.96 km</t>
         </is>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
+        <v>17</v>
+      </c>
+      <c r="O64" t="n">
+        <v>17</v>
+      </c>
+      <c r="P64" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
         <v>41</v>
       </c>
-      <c r="N64" t="n">
+      <c r="V64" t="n">
         <v>0</v>
       </c>
-      <c r="O64" t="n">
+      <c r="W64" t="n">
         <v>41</v>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4852,46 +6321,68 @@
           <t>9.01 km</t>
         </is>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
+        <v>22</v>
+      </c>
+      <c r="O65" t="n">
+        <v>22</v>
+      </c>
+      <c r="P65" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>-9</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
         <v>54</v>
       </c>
-      <c r="N65" t="n">
+      <c r="V65" t="n">
         <v>0</v>
       </c>
-      <c r="O65" t="n">
+      <c r="W65" t="n">
         <v>54</v>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -4922,26 +6413,48 @@
           <t>3.07 km</t>
         </is>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
+        <v>20</v>
+      </c>
+      <c r="O66" t="n">
+        <v>20</v>
+      </c>
+      <c r="P66" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
         <v>48</v>
       </c>
-      <c r="N66" t="n">
+      <c r="V66" t="n">
         <v>4</v>
       </c>
-      <c r="O66" t="n">
+      <c r="W66" t="n">
         <v>52</v>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4996,46 +6509,68 @@
           <t>2.83 km</t>
         </is>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
+        <v>11</v>
+      </c>
+      <c r="O67" t="n">
+        <v>11</v>
+      </c>
+      <c r="P67" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>-29</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
         <v>36</v>
       </c>
-      <c r="N67" t="n">
+      <c r="V67" t="n">
         <v>4</v>
       </c>
-      <c r="O67" t="n">
+      <c r="W67" t="n">
         <v>40</v>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -5066,26 +6601,48 @@
           <t>1.05 km</t>
         </is>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
+        <v>5</v>
+      </c>
+      <c r="O68" t="n">
+        <v>5</v>
+      </c>
+      <c r="P68" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>-40</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
         <v>23</v>
       </c>
-      <c r="N68" t="n">
+      <c r="V68" t="n">
         <v>10</v>
       </c>
-      <c r="O68" t="n">
+      <c r="W68" t="n">
         <v>33</v>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -5112,26 +6669,48 @@
           <t>7.74 km</t>
         </is>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>-12</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
         <v>23</v>
       </c>
-      <c r="N69" t="n">
+      <c r="V69" t="n">
         <v>0</v>
       </c>
-      <c r="O69" t="n">
+      <c r="W69" t="n">
         <v>23</v>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5186,46 +6765,68 @@
           <t>4.78 km</t>
         </is>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
+        <v>16</v>
+      </c>
+      <c r="O70" t="n">
+        <v>16</v>
+      </c>
+      <c r="P70" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-33</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
         <v>36</v>
       </c>
-      <c r="N70" t="n">
+      <c r="V70" t="n">
         <v>4</v>
       </c>
-      <c r="O70" t="n">
+      <c r="W70" t="n">
         <v>40</v>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -5256,26 +6857,48 @@
           <t>6.61 km</t>
         </is>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
+        <v>14</v>
+      </c>
+      <c r="O71" t="n">
+        <v>14</v>
+      </c>
+      <c r="P71" t="n">
         <v>36</v>
       </c>
-      <c r="N71" t="n">
+      <c r="Q71" t="n">
+        <v>-22</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>36</v>
+      </c>
+      <c r="V71" t="n">
         <v>0</v>
       </c>
-      <c r="O71" t="n">
+      <c r="W71" t="n">
         <v>36</v>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -5302,26 +6925,48 @@
           <t>9.58 km</t>
         </is>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
+        <v>11</v>
+      </c>
+      <c r="O72" t="n">
+        <v>11</v>
+      </c>
+      <c r="P72" t="n">
         <v>36</v>
       </c>
-      <c r="N72" t="n">
+      <c r="Q72" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>36</v>
+      </c>
+      <c r="V72" t="n">
         <v>0</v>
       </c>
-      <c r="O72" t="n">
+      <c r="W72" t="n">
         <v>36</v>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -5376,46 +7021,71 @@
           <t>1.81 km</t>
         </is>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
+        <v>31</v>
+      </c>
+      <c r="O73" t="n">
+        <v>31</v>
+      </c>
+      <c r="P73" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>-23</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U73" t="n">
         <v>58</v>
       </c>
-      <c r="N73" t="n">
+      <c r="V73" t="n">
         <v>10</v>
       </c>
-      <c r="O73" t="n">
+      <c r="W73" t="n">
         <v>68</v>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q73" s="4" t="inlineStr">
+      <c r="Y73" s="4" t="inlineStr">
         <is>
           <t>該当</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
         <is>
           <t>非該当</t>
         </is>
@@ -5446,26 +7116,48 @@
           <t>798 m</t>
         </is>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
+        <v>23</v>
+      </c>
+      <c r="O74" t="n">
+        <v>23</v>
+      </c>
+      <c r="P74" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>-13</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
         <v>48</v>
       </c>
-      <c r="N74" t="n">
+      <c r="V74" t="n">
         <v>15</v>
       </c>
-      <c r="O74" t="n">
+      <c r="W74" t="n">
         <v>63</v>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr"/>
@@ -5492,29 +7184,54 @@
           <t>2.86 km</t>
         </is>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
+        <v>20</v>
+      </c>
+      <c r="O75" t="n">
+        <v>20</v>
+      </c>
+      <c r="P75" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>不可 #4</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>有り</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U75" t="n">
         <v>58</v>
       </c>
-      <c r="N75" t="n">
+      <c r="V75" t="n">
         <v>4</v>
       </c>
-      <c r="O75" t="n">
+      <c r="W75" t="n">
         <v>62</v>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V75"/>
+  <autoFilter ref="A2:AD75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5525,7 +7242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5535,12 +7252,12 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>変電所スコア</t>
+          <t>空容量の読み方</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>系統スコア80点（S1空容量35/S2 N-1電制10/S3潮流15/S4出力制御5/S5配変10/S6エリア・実績5）</t>
+          <t>S1とゲートを決めるのは空容量。「上位系考慮」を優先し、無ければ</t>
         </is>
       </c>
     </row>
@@ -5548,7 +7265,7 @@
       <c r="A2" s="5" t="inlineStr"/>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>＋近接スコアS7 20点＝総合100点。substation.html と同じ計算。</t>
+          <t>「当該設備」で代用する（採用空容量の列がS1に使った値）。</t>
         </is>
       </c>
     </row>
@@ -5556,7 +7273,7 @@
       <c r="A3" s="5" t="inlineStr"/>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>ゲート除外・データ無の変電所は候補から外している（申し込み対象にならないため）。</t>
+          <t>採用空容量≦0 かつ N-1電制が「可」でない変電所はゲート除外となり、この表には出ない。</t>
         </is>
       </c>
     </row>
@@ -5564,7 +7281,7 @@
       <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>総合ランクは S:75以上 / A:60 / B:45。</t>
+          <t>空容量は各社の公表時点の値で、申し込み状況で変わる。実際の可否は接続検討の回答による。</t>
         </is>
       </c>
     </row>
@@ -5575,12 +7292,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>ハザード判定</t>
+          <t>変電所スコア</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>国土地理院「重ねるハザードマップ」のタイルを座標のピクセルで判定している。</t>
+          <t>系統スコア80点（S1空容量35/S2 N-1電制10/S3潮流15/S4出力制御5/S5配変10/S6エリア・実績5）</t>
         </is>
       </c>
     </row>
@@ -5588,7 +7305,7 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>タイルが無い区画＝その災害の公表区域が無い＝非該当。</t>
+          <t>＋近接スコアS7 20点＝総合100点。substation.html と同じ計算。</t>
         </is>
       </c>
     </row>
@@ -5596,7 +7313,7 @@
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>**非該当は「危険が無い」ではなく「公表された区域に入っていない」**。</t>
+          <t>ゲート除外・データ無の変電所は候補から外している（申し込み対象にならないため）。</t>
         </is>
       </c>
     </row>
@@ -5604,7 +7321,7 @@
       <c r="A9" s="5" t="inlineStr"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>整備範囲は自治体によって違うため、最終確認は自治体の窓口・図面で行うこと。</t>
+          <t>総合ランクは S:75以上 / A:60 / B:45。</t>
         </is>
       </c>
     </row>
@@ -5615,12 +7332,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>所在地の一致</t>
+          <t>ハザード判定</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>座標を国土地理院リバースジオコーダで引き、入力の地番と突き合わせた参考値。</t>
+          <t>国土地理院「重ねるハザードマップ」のタイルを座標のピクセルで判定している。</t>
         </is>
       </c>
     </row>
@@ -5628,37 +7345,77 @@
       <c r="A12" s="5" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>「要確認」は座標か地番のどちらかがずれている可能性を示す。</t>
+          <t>タイルが無い区画＝その災害の公表区域が無い＝非該当。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>**非該当は「危険が無い」ではなく「公表された区域に入っていない」**。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>この表に無いもの</t>
-        </is>
-      </c>
+      <c r="A14" s="5" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>用途地域・市街化区域/調整区域・液状化・自然公園などの許認可17項目は</t>
+          <t>整備範囲は自治体によって違うため、最終確認は自治体の窓口・図面で行うこと。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>所在地の一致</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>座標を国土地理院リバースジオコーダで引き、入力の地番と突き合わせた参考値。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>「要確認」は座標か地番のどちらかがずれている可能性を示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>この表に無いもの</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>用途地域・市街化区域/調整区域・液状化・自然公園などの許認可17項目は</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>reinfolib のAPIキーが要るため含めていない（scripts/reinfolib_judge.py）。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>座標が確定しているので、キーがあればそのまま自動判定できる。</t>
         </is>
